--- a/artfynd/A 27502-2024 artfynd.xlsx
+++ b/artfynd/A 27502-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>118496661</v>
       </c>
       <c r="B2" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>118496734</v>
       </c>
       <c r="B3" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 27502-2024 artfynd.xlsx
+++ b/artfynd/A 27502-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118496661</v>
+        <v>118496734</v>
       </c>
       <c r="B2" t="n">
         <v>97853</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>631857</v>
+        <v>631748</v>
       </c>
       <c r="R2" t="n">
-        <v>6646151</v>
+        <v>6646258</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -763,7 +763,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ca 25 bladrosetter.</t>
+          <t>5 bladrosetter.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118496734</v>
+        <v>118497118</v>
       </c>
       <c r="B3" t="n">
-        <v>97853</v>
+        <v>57443</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,25 +803,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -829,23 +829,31 @@
           <t>5</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Skulla Krakmosse, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>631748</v>
+        <v>631863</v>
       </c>
       <c r="R3" t="n">
-        <v>6646258</v>
+        <v>6646092</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,7 +887,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>5 bladrosetter.</t>
+          <t>Födosökande grupp av talltitor.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -888,7 +896,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -907,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118497118</v>
+        <v>118496661</v>
       </c>
       <c r="B4" t="n">
-        <v>57443</v>
+        <v>97853</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,57 +926,49 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Skulla Krakmosse, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>631863</v>
+        <v>631857</v>
       </c>
       <c r="R4" t="n">
-        <v>6646092</v>
+        <v>6646151</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1003,7 +1002,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Födosökande grupp av talltitor.</t>
+          <t>Ca 25 bladrosetter.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1012,6 +1011,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 27502-2024 artfynd.xlsx
+++ b/artfynd/A 27502-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1028,6 +1028,1172 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128551513</v>
+      </c>
+      <c r="B5" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Skulla Krakmosse, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>631769</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6646253</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>18:46</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>18:46</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Ki Mähler</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Ki Mähler</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128511696</v>
+      </c>
+      <c r="B6" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Skiljepussen, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>631725</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6646303</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>18:32</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>18:32</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Ki Mähler</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Ki Mähler</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128511695</v>
+      </c>
+      <c r="B7" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Skiljepussen, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>631750</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6646288</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>18:42</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>18:42</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Ki Mähler</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Ki Mähler</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128511694</v>
+      </c>
+      <c r="B8" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Skiljepussen, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>631764</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6646285</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>18:47</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>18:47</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Ki Mähler</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Ki Mähler</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128511702</v>
+      </c>
+      <c r="B9" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Skiljepussen, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>631730</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6646274</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>18:42</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>18:42</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Ki Mähler</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Ki Mähler</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128511692</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57682</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Skulla Krakmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>631759</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6646255</v>
+      </c>
+      <c r="S10" t="n">
+        <v>20</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Ki Mähler</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Ki Mähler</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>128511700</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57682</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Skulla Krakmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>631768</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6646254</v>
+      </c>
+      <c r="S11" t="n">
+        <v>20</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>18:46</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>18:46</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Ki Mähler</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Ki Mähler</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>128511691</v>
+      </c>
+      <c r="B12" t="n">
+        <v>58055</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Skulla Krakmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>631753</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6646240</v>
+      </c>
+      <c r="S12" t="n">
+        <v>20</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>19:11</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>19:11</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Ki Mähler</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Ki Mähler</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>128511693</v>
+      </c>
+      <c r="B13" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Skulla Krakmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>631768</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6646253</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>18:59</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>18:59</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Ki Mähler</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Ki Mähler</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>128511697</v>
+      </c>
+      <c r="B14" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Skulla Krakmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>631770</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6646245</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>18:52</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Slog ihop två fyndtillfällen till ett, därav bilder från olika datum.</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Ki Mähler</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Ki Mähler</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 27502-2024 artfynd.xlsx
+++ b/artfynd/A 27502-2024 artfynd.xlsx
@@ -1150,7 +1150,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128511696</v>
+        <v>128511695</v>
       </c>
       <c r="B6" t="n">
         <v>98571</v>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>631725</v>
+        <v>631750</v>
       </c>
       <c r="R6" t="n">
-        <v>6646303</v>
+        <v>6646288</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1229,7 +1229,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1266,7 +1266,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128511695</v>
+        <v>128511696</v>
       </c>
       <c r="B7" t="n">
         <v>98571</v>
@@ -1310,10 +1310,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>631750</v>
+        <v>631725</v>
       </c>
       <c r="R7" t="n">
-        <v>6646288</v>
+        <v>6646303</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1345,7 +1345,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18:42</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1355,7 +1355,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>18:42</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1848,48 +1848,57 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128511691</v>
+        <v>128511693</v>
       </c>
       <c r="B12" t="n">
-        <v>58055</v>
+        <v>98571</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Skulla Krakmossen, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>631753</v>
+        <v>631768</v>
       </c>
       <c r="R12" t="n">
-        <v>6646240</v>
+        <v>6646253</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1918,7 +1927,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>18:59</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1928,7 +1937,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>18:59</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1955,57 +1964,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128511693</v>
+        <v>128511691</v>
       </c>
       <c r="B13" t="n">
-        <v>98571</v>
+        <v>58055</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Skulla Krakmossen, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>631768</v>
+        <v>631753</v>
       </c>
       <c r="R13" t="n">
-        <v>6646253</v>
+        <v>6646240</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>18:59</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>18:59</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 27502-2024 artfynd.xlsx
+++ b/artfynd/A 27502-2024 artfynd.xlsx
@@ -1030,7 +1030,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128551513</v>
+        <v>128511695</v>
       </c>
       <c r="B5" t="n">
         <v>98571</v>
@@ -1060,7 +1060,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1068,19 +1068,16 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Skulla Krakmosse, Upl</t>
+          <t>Skiljepussen, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>631769</v>
+        <v>631750</v>
       </c>
       <c r="R5" t="n">
-        <v>6646253</v>
+        <v>6646288</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1107,22 +1104,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>18:46</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>18:46</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1131,7 +1128,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1150,7 +1146,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128511695</v>
+        <v>128511696</v>
       </c>
       <c r="B6" t="n">
         <v>98571</v>
@@ -1194,10 +1190,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>631750</v>
+        <v>631725</v>
       </c>
       <c r="R6" t="n">
-        <v>6646288</v>
+        <v>6646303</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1229,7 +1225,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>18:42</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1239,7 +1235,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>18:42</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1266,7 +1262,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128511696</v>
+        <v>128551513</v>
       </c>
       <c r="B7" t="n">
         <v>98571</v>
@@ -1296,7 +1292,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>63</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1304,16 +1300,19 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Skiljepussen, Upl</t>
+          <t>Skulla Krakmosse, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>631725</v>
+        <v>631769</v>
       </c>
       <c r="R7" t="n">
-        <v>6646303</v>
+        <v>6646253</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1340,22 +1339,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1364,6 +1363,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1848,57 +1848,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128511693</v>
+        <v>128511691</v>
       </c>
       <c r="B12" t="n">
-        <v>98571</v>
+        <v>58055</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Skulla Krakmossen, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>631768</v>
+        <v>631753</v>
       </c>
       <c r="R12" t="n">
-        <v>6646253</v>
+        <v>6646240</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1927,7 +1918,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>18:59</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1937,7 +1928,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>18:59</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1964,48 +1955,57 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128511691</v>
+        <v>128511693</v>
       </c>
       <c r="B13" t="n">
-        <v>58055</v>
+        <v>98571</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Skulla Krakmossen, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>631753</v>
+        <v>631768</v>
       </c>
       <c r="R13" t="n">
-        <v>6646240</v>
+        <v>6646253</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>18:59</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>18:59</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 27502-2024 artfynd.xlsx
+++ b/artfynd/A 27502-2024 artfynd.xlsx
@@ -1030,10 +1030,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128511695</v>
+        <v>128551513</v>
       </c>
       <c r="B5" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>63</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1068,16 +1068,19 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Skiljepussen, Upl</t>
+          <t>Skulla Krakmosse, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>631750</v>
+        <v>631769</v>
       </c>
       <c r="R5" t="n">
-        <v>6646288</v>
+        <v>6646253</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1104,22 +1107,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>18:42</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>18:42</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,6 +1131,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1146,10 +1150,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128511696</v>
+        <v>128511695</v>
       </c>
       <c r="B6" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1190,10 +1194,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>631725</v>
+        <v>631750</v>
       </c>
       <c r="R6" t="n">
-        <v>6646303</v>
+        <v>6646288</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1225,7 +1229,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1235,7 +1239,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1262,10 +1266,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128551513</v>
+        <v>128511696</v>
       </c>
       <c r="B7" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1292,7 +1296,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1300,19 +1304,16 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Skulla Krakmosse, Upl</t>
+          <t>Skiljepussen, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>631769</v>
+        <v>631725</v>
       </c>
       <c r="R7" t="n">
-        <v>6646253</v>
+        <v>6646303</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1339,22 +1340,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18:46</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>18:46</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1363,7 +1364,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1385,7 +1385,7 @@
         <v>128511694</v>
       </c>
       <c r="B8" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>128511702</v>
       </c>
       <c r="B9" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1617,7 +1617,7 @@
         <v>128511692</v>
       </c>
       <c r="B10" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1736,7 +1736,7 @@
         <v>128511700</v>
       </c>
       <c r="B11" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1848,48 +1848,57 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128511691</v>
+        <v>128511693</v>
       </c>
       <c r="B12" t="n">
-        <v>58055</v>
+        <v>98579</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Skulla Krakmossen, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>631753</v>
+        <v>631768</v>
       </c>
       <c r="R12" t="n">
-        <v>6646240</v>
+        <v>6646253</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1918,7 +1927,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>18:59</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1928,7 +1937,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>18:59</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1955,57 +1964,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128511693</v>
+        <v>128511691</v>
       </c>
       <c r="B13" t="n">
-        <v>98571</v>
+        <v>58059</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Skulla Krakmossen, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>631768</v>
+        <v>631753</v>
       </c>
       <c r="R13" t="n">
-        <v>6646253</v>
+        <v>6646240</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>18:59</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>18:59</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2074,7 +2074,7 @@
         <v>128511697</v>
       </c>
       <c r="B14" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 27502-2024 artfynd.xlsx
+++ b/artfynd/A 27502-2024 artfynd.xlsx
@@ -1033,7 +1033,7 @@
         <v>128551513</v>
       </c>
       <c r="B5" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         <v>128511695</v>
       </c>
       <c r="B6" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>128511696</v>
       </c>
       <c r="B7" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>128511694</v>
       </c>
       <c r="B8" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>128511702</v>
       </c>
       <c r="B9" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1848,57 +1848,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128511693</v>
+        <v>128511691</v>
       </c>
       <c r="B12" t="n">
-        <v>98579</v>
+        <v>58059</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Skulla Krakmossen, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>631768</v>
+        <v>631753</v>
       </c>
       <c r="R12" t="n">
-        <v>6646253</v>
+        <v>6646240</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1927,7 +1918,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>18:59</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1937,7 +1928,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>18:59</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1964,48 +1955,57 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128511691</v>
+        <v>128511693</v>
       </c>
       <c r="B13" t="n">
-        <v>58059</v>
+        <v>98585</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Skulla Krakmossen, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>631753</v>
+        <v>631768</v>
       </c>
       <c r="R13" t="n">
-        <v>6646240</v>
+        <v>6646253</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>18:59</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>18:59</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2074,7 +2074,7 @@
         <v>128511697</v>
       </c>
       <c r="B14" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 27502-2024 artfynd.xlsx
+++ b/artfynd/A 27502-2024 artfynd.xlsx
@@ -1033,7 +1033,7 @@
         <v>128551513</v>
       </c>
       <c r="B5" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         <v>128511695</v>
       </c>
       <c r="B6" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>128511696</v>
       </c>
       <c r="B7" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>128511694</v>
       </c>
       <c r="B8" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>128511702</v>
       </c>
       <c r="B9" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>128511693</v>
       </c>
       <c r="B13" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>128511697</v>
       </c>
       <c r="B14" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 27502-2024 artfynd.xlsx
+++ b/artfynd/A 27502-2024 artfynd.xlsx
@@ -1030,10 +1030,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128551513</v>
+        <v>128511695</v>
       </c>
       <c r="B5" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1068,19 +1068,16 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Skulla Krakmosse, Upl</t>
+          <t>Skiljepussen, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>631769</v>
+        <v>631750</v>
       </c>
       <c r="R5" t="n">
-        <v>6646253</v>
+        <v>6646288</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1107,22 +1104,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>18:46</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>18:46</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1131,7 +1128,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1150,10 +1146,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128511695</v>
+        <v>128511696</v>
       </c>
       <c r="B6" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1194,10 +1190,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>631750</v>
+        <v>631725</v>
       </c>
       <c r="R6" t="n">
-        <v>6646288</v>
+        <v>6646303</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1229,7 +1225,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>18:42</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1239,7 +1235,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>18:42</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1266,10 +1262,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128511696</v>
+        <v>128551513</v>
       </c>
       <c r="B7" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1296,7 +1292,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>63</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1304,16 +1300,19 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Skiljepussen, Upl</t>
+          <t>Skulla Krakmosse, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>631725</v>
+        <v>631769</v>
       </c>
       <c r="R7" t="n">
-        <v>6646303</v>
+        <v>6646253</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1340,22 +1339,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1364,6 +1363,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1385,7 +1385,7 @@
         <v>128511694</v>
       </c>
       <c r="B8" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>128511702</v>
       </c>
       <c r="B9" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>128511693</v>
       </c>
       <c r="B13" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>128511697</v>
       </c>
       <c r="B14" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
